--- a/DXLibProject_Start/Data/CSV/ActionEffectParam.xlsx
+++ b/DXLibProject_Start/Data/CSV/ActionEffectParam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78266E8F-ED97-4184-B179-31DF3479E29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1BB217B-3456-44F3-A289-B129414AA389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5700" yWindow="-13365" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6045" yWindow="-13020" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,21 +40,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>comment</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>ID</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>maxSecond</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>interval</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -422,13 +414,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="12.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -438,14 +430,8 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:3">
       <c r="A2" t="str">
         <f>VLOOKUP(VALUE(B2)+1000,[1]Item!$A:$B,2,FALSE)</f>
         <v>回復瓶S</v>
@@ -454,16 +440,10 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>0.3</v>
-      </c>
-      <c r="E2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:3">
       <c r="A3" t="str">
         <f>VLOOKUP(VALUE(B3)+1000,[1]Item!$A:$B,2,FALSE)</f>
         <v>火炎瓶S</v>
@@ -472,12 +452,6 @@
         <v>100</v>
       </c>
       <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>0.5</v>
-      </c>
-      <c r="E3">
         <v>1</v>
       </c>
     </row>

--- a/DXLibProject_Start/Data/CSV/ActionEffectParam.xlsx
+++ b/DXLibProject_Start/Data/CSV/ActionEffectParam.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1BB217B-3456-44F3-A289-B129414AA389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5044CA08-ECF6-439D-ADED-7845A54AFBEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6045" yWindow="-13020" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6555" yWindow="3255" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,18 +37,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+  <si>
+    <t>ID</t>
+  </si>
   <si>
     <t>comment</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ID</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>power</t>
-    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HPを2回復</t>
+  </si>
+  <si>
+    <t>1ダメージを与える</t>
   </si>
 </sst>
 </file>
@@ -94,8 +94,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -111,44 +114,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Item"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>ID</v>
-          </cell>
-          <cell r="B1" t="str">
-            <v>text</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="A2">
-            <v>1000</v>
-          </cell>
-          <cell r="B2" t="str">
-            <v>回復瓶S</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3">
-            <v>1100</v>
-          </cell>
-          <cell r="B3" t="str">
-            <v>火炎瓶S</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -418,40 +383,39 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="str">
-        <f>VLOOKUP(VALUE(B2)+1000,[1]Item!$A:$B,2,FALSE)</f>
-        <v>回復瓶S</v>
-      </c>
-      <c r="B2">
+      <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="C2">
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="str">
-        <f>VLOOKUP(VALUE(B3)+1000,[1]Item!$A:$B,2,FALSE)</f>
-        <v>火炎瓶S</v>
-      </c>
-      <c r="B3">
-        <v>100</v>
-      </c>
-      <c r="C3">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1">
         <v>1</v>
       </c>
     </row>
